--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_116_Cambodia.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_116_Cambodia.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rf80042dd78904815"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R337fb5c58bce4c9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R6688cb448f0b4bb6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R1a7ba2e9b0154f25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R1b47aa617fce40e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R88c2d3b612154672"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R0839278508c5409d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R2b29db786f7a4dde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R1560db81d7444cc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rbccda55f132a4034"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R86cf6c3104df4d53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rd9ae42bfe29744e3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ116CommercialTable" displayName="EEZ116CommercialTable" ref="A1:O10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O10"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ116CommercialTable" displayName="EEZ116CommercialTable" ref="A1:E10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E10"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ116FunctionalTable" displayName="EEZ116FunctionalTable" ref="A1:O21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O21"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ116FunctionalTable" displayName="EEZ116FunctionalTable" ref="A1:E21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E21"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ116ValidationTable" displayName="EEZ116ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ116ValidationTable" displayName="EEZ116ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -8064,7 +8018,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb87cb3a3a8144033"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb13f070273624db7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8074,20 +8028,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -8095,552 +8039,193 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>8609.3782384851</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.4116477952853503</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>258.01668747768264</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>8609.3782384851</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>261.6090204236103</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$111,A2,'Species'!$U$2:$U$111))</x:f>
-        <x:v>2252291.0074264347</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.4116477952853503</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>258.01668747768264</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>2221363.254336372</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>30927.753090062644</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0139228705749443</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.013922870574944417</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>35904.8160475086</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.2924875681142374</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>196.10450388271735</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>35904.8160475086</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>251.62013841280995</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$111,A3,'Species'!$U$2:$U$111))</x:f>
-        <x:v>9034374.783560593</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.2924875681142374</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>196.10450388271735</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>7041096.137996902</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>1993278.645563691</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.2830920934039045</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.2830920934039046</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>20.8492273084</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.832775892726762</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>680.4181545823517</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>20.8492273084</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>769.2953672222228</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$111,A4,'Species'!$U$2:$U$111))</x:f>
-        <x:v>16039.213978515174</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.832775892726762</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>680.4181545823517</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>14186.192769649499</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1853.0212088656754</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.130621459820432</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.13062145982043202</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>8141.025148114799</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.135569587093262</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>136.63739925344268</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>8141.025148114799</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>145.96402562924504</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$111,A5,'Species'!$U$2:$U$111))</x:f>
-        <x:v>1188296.803367757</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.135569587093262</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>136.63739925344268</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>1112368.503495279</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>75928.299872478</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0682582252499027</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.06825822524990277</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>11575.5589500022</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.0990356102218306</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>12.561329568050239</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>11575.5589500022</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>12.564283615897414</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$111,A6,'Species'!$U$2:$U$111))</x:f>
-        <x:v>145438.60566036732</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.0990356102218306</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>12.561329568050239</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>145404.41090537122</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>34.194754996104166</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0002351699978231</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.00023516999782322983</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>32083.8489645257</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.4998210623088726</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>316.09750092434643</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>32083.8489645257</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>578.520052923559</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$111,A7,'Species'!$U$2:$U$111))</x:f>
-        <x:v>18561150.00094888</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.4998210623088726</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>316.09750092434643</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>10141624.477720754</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>8419525.523228126</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.8301949595673004</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.8301949595673004</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>114812.8541388191</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.810765087578992</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>646.7926671823502</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>114812.8541388191</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1098.0237933695387</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$111,A8,'Species'!$U$2:$U$111))</x:f>
-        <x:v>126067245.62908967</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.810765087578992</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>646.7926671823502</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>74260112.15526494</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>51807133.473824725</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.697644158757868</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.6976441587578678</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>589.4981629456998</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.8968287828698633</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>788.5491771159102</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>589.4981629456998</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>790.302610930591</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$111,A9,'Species'!$U$2:$U$111))</x:f>
-        <x:v>465881.93731477356</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.8968287828698633</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>788.5491771159102</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>464848.29130217235</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>1033.6460126012098</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0022236201185244</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.002223620118524418</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>9.155609932399999</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.7974999878898297</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>627.3356784909721</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>9.155609932399999</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>665.0615354216444</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$111,A10,'Species'!$U$2:$U$111))</x:f>
-        <x:v>6089.043999363601</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.7974999878898297</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>627.3356784909721</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>5743.640768940837</x:v>
       </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>345.40323042276395</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0601366353359976</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.0601366353359976</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G10">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O10">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb855b9d9bdfa466f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R192c5e34e4af4dec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8650,20 +8235,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -8671,1146 +8246,402 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>2632.0744429388997</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.6346608770766546</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>431.1822526288121</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>2632.0744429388997</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>444.7128974950848</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$111,A2,'Species'!$U$2:$U$111))</x:f>
-        <x:v>1170517.4519421193</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.6346608770766546</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>431.1822526288121</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>1134903.7873931204</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>35613.66454899893</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0313803380908646</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.031380338090864685</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>32.4353749337</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.46</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>288.40315031266056</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>32.4353749337</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$111,A3,'Species'!$U$2:$U$111))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>9354.464312451382</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.46</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>9354.464312451382</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>139.4545761275</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.3558806474588625</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2269.241134736632</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>139.4545761275</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2325.591831429262</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$111,A4,'Species'!$U$2:$U$111))</x:f>
-        <x:v>324314.4230975442</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.3558806474588625</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2269.241134736632</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>316456.0605757841</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>7858.362521760049</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0248323969762563</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.024832396976256197</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>13.932162892300001</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.373777874332354</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2364.7099259086795</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>13.932162892300001</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2365.625065058238</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$111,A5,'Species'!$U$2:$U$111))</x:f>
-        <x:v>32958.27374849916</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.373777874332354</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2364.7099259086795</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>32945.52388079839</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>12.749867700767936</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0003869984810956</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.00038699848109560427</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>375.64339299950007</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.4410795857761975</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2761.083786809891</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>375.64339299950007</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2788.0609264132354</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$111,A6,'Species'!$U$2:$U$111))</x:f>
-        <x:v>1047316.6662871971</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.4410795857761975</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2761.083786809891</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>1037182.8820331758</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>10133.78425402136</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0097704893028665</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.00977048930286647</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>7.005429147899999</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.7200000000000006</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>524.8074602497734</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>7.005429147899999</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>524.8074602497728</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$111,A7,'Species'!$U$2:$U$111))</x:f>
-        <x:v>3676.501479069129</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.7200000000000006</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>524.8074602497734</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>3676.5014790691325</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>-3.637978807091713e-12</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>0.999999999999999</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>-9.895219212621741e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>80.3777783907</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.2438418079105396</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>175.32417658958644</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>80.3777783907</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>249.74998243055043</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$111,A8,'Species'!$U$2:$U$111))</x:f>
-        <x:v>20074.348740884</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.2438418079105396</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>175.32417658958644</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>14092.167812449732</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>5982.180928434269</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.4245039519859612</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.4245039519859612</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>2.1501807845000003</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.05</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1122.018454301963</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>2.1501807845000003</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1122.018454301963</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$111,A9,'Species'!$U$2:$U$111))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>2412.5425202944725</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.05</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1122.018454301963</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>2412.5425202944725</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>17009.707400001498</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.403611192780996</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>253.28600425553816</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>17009.707400001498</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>279.9476734281211</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$111,A10,'Species'!$U$2:$U$111))</x:f>
-        <x:v>4761828.012323515</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.403611192780996</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>253.28600425553816</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>4308320.820902239</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>453507.19142127596</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.1052630967547825</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.10526309675478242</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>45.337315463299994</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>2.964022048342841</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>92.04963024940282</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>45.337315463299994</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>95.63419610520181</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$111,A11,'Species'!$U$2:$U$111))</x:f>
-        <x:v>4335.79771790063</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>2.964022048342841</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>92.04963024940282</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>4173.283124897298</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>162.51459300333227</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0389416649049736</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.03894166490497374</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>27364.779749671598</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.534521358845093</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>342.3902261548687</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>27364.779749671598</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>645.8312597560874</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$111,A12,'Species'!$U$2:$U$111))</x:f>
-        <x:v>17673030.178678278</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.534521358845093</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>342.3902261548687</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>9369433.127168229</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>8303597.051510049</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.8862432698764229</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.8862432698764229</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>53526.9433563246</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.245888762522619</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>1761.5248026586123</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>53526.9433563246</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1784.2850410729868</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$111,A13,'Species'!$U$2:$U$111))</x:f>
-        <x:v>95507324.32505107</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.245888762522619</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>1761.5248026586123</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>94289038.33266841</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>1218285.9923826605</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.012920759548786</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.01292075954878585</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>7987.2499339183005</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.505434058457244</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>320.20938645495505</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>7987.2499339183005</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>981.38663571388</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$111,A14,'Species'!$U$2:$U$111))</x:f>
-        <x:v>7838580.341253991</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.505434058457244</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>320.20938645495505</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>2557592.4008023595</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>5280987.940451631</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>3.0648278196302496</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>2.0648278196302496</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>11589.922814539199</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.0994457879026847</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>12.573198958848131</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>11589.922814539199</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>12.582069475962031</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$111,A15,'Species'!$U$2:$U$111))</x:f>
-        <x:v>145825.2140735696</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.0994457879026847</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>12.573198958848131</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>145722.40546489446</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>102.80860867514275</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0007055099615405</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.0007055099615406092</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>18895.108647507102</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.192452136930911</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>155.7586365664321</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>18895.108647507102</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>226.11919576343735</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$111,A16,'Species'!$U$2:$U$111))</x:f>
-        <x:v>4272546.771237076</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.192452136930911</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>155.7586365664321</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>2943076.360710307</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>1329470.4105267692</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.4517281400764959</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.45172814007649587</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>38095.5176020039</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.2399624509108076</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>173.7650585031718</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>38095.5176020039</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>173.76816941572147</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$111,A17,'Species'!$U$2:$U$111))</x:f>
-        <x:v>6619788.356644613</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.2399624509108076</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>173.7650585031718</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>6619669.844820818</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>118.51182379480451</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0000179029810508</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.000017902981050864236</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>2572.003956845401</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.515866419911493</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>327.99439323834247</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>2572.003956845401</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>329.79012441491716</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$111,A18,'Species'!$U$2:$U$111))</x:f>
-        <x:v>848221.504923704</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.515866419911493</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>327.99439323834247</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>843602.8772321232</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>4618.627691580798</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0054748837589726</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.005474883758972707</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>24209.588047702004</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.5654458687554498</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>367.6595647734426</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>24209.588047702004</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>649.6983628884411</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$111,A19,'Species'!$U$2:$U$111))</x:f>
-        <x:v>15728929.720795564</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.5654458687554498</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>367.6595647734426</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>8900886.604962457</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>6828043.115833107</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.7671194363970788</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.7671194363970787</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>7146.9030981417</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.3279562246136813</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>212.7924547715273</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>7146.9030981417</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>239.2271020136079</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$111,A20,'Species'!$U$2:$U$111))</x:f>
-        <x:v>1709732.9165405147</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.3279562246136813</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>212.7924547715273</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>1520807.054267806</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>188925.86227270868</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.1242273710807236</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.12422737108072346</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>20.8492273084</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.832775892726762</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>680.4181545823517</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>20.8492273084</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>769.2953672222228</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$111,A21,'Species'!$U$2:$U$111))</x:f>
-        <x:v>16039.213978515174</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.832775892726762</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>680.4181545823517</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>14186.192769649499</x:v>
       </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>1853.0212088656754</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.130621459820432</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.13062145982043202</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G21">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O21">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d3636d30ca04cf9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb54ed97753574b8b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9985,7 +8816,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -10084,7 +8915,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>157736807.02534643</x:v>
+        <x:v>95406747.0645604</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10098,7 +8929,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>157736807.0253464</x:v>
+        <x:v>134067533.23490132</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10112,7 +8943,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-62330059.96078603</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10126,7 +8957,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-2.9802322387695312e-8</x:v>
+        <x:v>-23669273.790445104</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10137,9 +8968,9 @@
         <x:v>EEZ_116</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -10151,47 +8982,19 @@
         <x:v>EEZ_116</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_116</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_116</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0eed92b424b649d5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R299bfb76593b44bc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10238,7 +9041,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
